--- a/data/daily/2026-10/2026-10-29.xlsx
+++ b/data/daily/2026-10/2026-10-29.xlsx
@@ -1545,7 +1545,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 로네펠트 기프트 에디션 (티백 5종증정)</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 단독 기프트박스 증정 (공식수입)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>35,900원</t>
+          <t>34,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1565,29 +1565,29 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261027092029_af14b962a57c4de9940654af7e1928f7.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261029082837_60ff4c7ff31442b5a4b9bb3e2a571288.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16366</v>
+        <v>16368</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>우수한 피로 회복 효과 — 피로 누적 시 아침에 섭취하면 하루 종일 지치지 않는 우수한 체감을 제공함.</t>
+          <t>우수한 피로 회복 효과 — 피로 누적 시 아침 식후 복용 시 하루 종일 활력 유지 효과 체감</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>고급스러운 포장 디자인 — 패키지 포장이 고급스러워 생일이나 특별한 날 선물용으로 적절함.</t>
+          <t>고급 포장 및 빠른 배송 — 패키지 포장이 고급스럽고 배송이 깔끔하며 속도가 빠름</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>공복 섭취 시 속쓰림 발생 — 고함량 제품 특성상 공복에 복용 시 속쓰림이나 울렁거림이 심하게 발생할 수 있음.</t>
+          <t>공복 복용 시 위장 장애 — 고함량 영양제 특성상 빈속에 먹으면 속쓰림이나 울렁거림 발생 가능</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -1631,24 +1631,28 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15709</v>
+        <v>15710</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>자극 없는 목넘김과 맛 — 영양제 신맛이 강하지 않고 목넘김이 부드러워 섭취하기 편함.</t>
+          <t>간편한 휴대 및 복용 — 액상과 정제 결합 포장으로 어디서나 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>피로 회복 및 활력 충전 — 피로할 때 복용하면 활력이 충전되고 구내염 개선에 도움을 줌.</t>
+          <t>부드러운 목넘김과 풍미 — 신맛이 강하지 않고 알약 섭취 시 목넘김이 부드러움</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>세련된 디자인과 휴대성 — 디자인이 세련되고 통 형태로 되어 있어 휴대하며 챙겨 먹기 유용함.</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>피로 개선 및 구내염 완화 — 피로 회복과 몸 상태 개선, 구내염 완화에 도움을 줌</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>단기 복용 시 미미한 체감 — 며칠 안 먹은 초기에는 즉각적인 변화 효과 체감이 적을 수 있음</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
@@ -1690,21 +1694,21 @@
         <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>3427</v>
+        <v>3429</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>넉넉한 용량과 온가족 섭취 — 용량이 넉넉하여 온 가족이 함께 나누어 먹기에 적합함.</t>
+          <t>하루 한 병의 간편한 섭취 — 여러 영양제를 별도로 챙길 필요 없이 하루 한 병으로 해결됨</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>확실한 활력 증진 효과 — 에너지를 올려주고 체력이 달릴 때 확실하게 힘이 나는 효과가 있음.</t>
+          <t>진한 액상과 에너지 충전 — 액상 농도가 매우 진하며 지칠 때 먹으면 피로 회복 체감이 뛰어남</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>진한 액상 농도 — 타 액상 제품에 비해 농도가 확실히 진하여 품질 만족도가 높음.</t>
+          <t>넉넉한 용량 구성 — 30+3입 구성으로 한 달 이상 온 가족이 충분히 복용 가능함</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1753,12 +1757,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>맛있고 간편한 젤리 형태 — 물 없이 간식처럼 씹어 먹는 새콤달콤한 젤리 형태로 섭취가 간편함.</t>
+          <t>물 없이 먹는 젤리 타입 — 알약과 달리 물 없이 간식처럼 씹어 먹을 수 있어 편함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>꾸준한 영양 관리 용이 — 영양제 먹는 것을 자주 잊는 사람도 매일 부담 없이 챙겨 먹기 좋음.</t>
+          <t>새콤달콤하고 맛있는 풍미 — 은은한 단맛과 새콤달콤함으로 매일 맛있게 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -1777,50 +1781,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 슬리브 기프트 에디션 (공식수입)</t>
+          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>뉴트리포유</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>43,900원</t>
+          <t>19,900원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11866425</t>
+          <t>https://gift.kakao.com/product/10056171</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261015103203_b8bc495679ff4e64935331509be98c02.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260219100848_1c2cc8073bd44eaab9f09d6b8fb8f34c.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>835</v>
+        <v>8769</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>효과적인 피로 회복 — 피로 회복에 도움을 주며 환절기 체력 관리에 효과적임.</t>
+          <t>합리적인 가격과 빠른 배송 — 좋은 제품을 착한 가격에 구매 가능하며 빠른 배송이 이뤄짐</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>알약과 액상 이중 제형 — 알약과 액상이 함께 구성되어 한 번에 간편하고 효과적인 섭취가 가능함.</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>만족스러운 선물 구성 — 제품 구성과 배송 상태가 만족스러워 선물용으로 적합함.</t>
-        </is>
-      </c>
+          <t>간편한 활력 충전 — 하루를 시작할 때 간편하게 복용하여 활력과 체력을 챙기기 좋음</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -1836,43 +1836,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 슬리브 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>뉴트리포유</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19,900원</t>
+          <t>43,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10056171</t>
+          <t>https://gift.kakao.com/product/11866425</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260219100848_1c2cc8073bd44eaab9f09d6b8fb8f34c.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261015103203_b8bc495679ff4e64935331509be98c02.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>8768</v>
+        <v>835</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>신속하고 안전한 배송 — 주문 후 제품 배송이 매우 빠르고 안전하게 도착함.</t>
+          <t>정제와 액상의 이중 제형 — 알약과 액상 비타민이 함께 들어있어 높은 효과가 느껴짐</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>간편한 피로 및 체력 관리 — 아침 출근길이나 피곤할 때 간편하게 먹고 활력을 얻기 좋음.</t>
+          <t>환절기 피로 회복 체감 — 환절기 건강 관리 및 피로 회복에 빠른 체감 효과를 선사함</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -1918,23 +1918,19 @@
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>1818</v>
+        <v>1820</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>신기한 분말 혼합 제형 — 버튼을 눌러 분말을 액상에 풀어 마시는 신기한 방식임.</t>
+          <t>목걸림 없는 분말 제형 — 알약과 달리 분말을 액상에 풀어 마셔 목에 걸리는 불편함이 없음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>우수한 휴대성과 간편함 — 가방에 넣어 다니다가 피곤할 때 간편하게 챙겨 먹기 유용함.</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>고급스러운 브랜드 이미지 — 정관장 브랜드로 포장과 분위기가 고급스러워 선물용으로 적합함.</t>
-        </is>
-      </c>
+          <t>우수한 휴대성과 활력 증진 — 가방에 넣어 다니기 좋으며 피곤할 때 복용 시 에너지 생성을 도움</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -1981,23 +1977,23 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>개별 포장의 우수한 휴대성 — 컴팩트한 포 포장으로 여행이나 외출 시 가방에 들고 다니기 좋음.</t>
+          <t>휴대가 용이한 포장 형태 — 개별 포 형태로 제작되어 여행이나 외출 시 휴대가 매우 편리함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>체력 증진 및 활력 제공 — 꾸준히 복용 시 활력이 생기고 피로 해소에 도움을 줌.</t>
+          <t>지속 복용 시 에너지 개선 — 일주일 정도 꾸준히 섭취 시 몸에 활력이 생기는 것을 체감함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>배송 중 박스 구겨짐 — 배송 과정에서 박스가 다 구겨져서 도착한 점이 아쉬움.</t>
+          <t>배송 상자 구겨짐 발생 — 배송 과정 중에 제품 외관 박스가 구겨져서 도착하는 문제 있음</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>아쉬운 사은품 품질 — 함께 제공된 사은품의 품질이 기대에 미치지 못함.</t>
+          <t>아쉬운 사은품 품질 — 동봉되어 오는 사은품이 저가형 제품으로 제공되어 다소 아쉬움</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -2044,18 +2040,18 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>빠르고 안전한 배송 — 배송 상태가 양호하고 신속하게 도착함.</t>
+          <t>확실한 활력 증진 효과 — 바쁘고 피로할 때 복용 시 몸에 활력이 돋는 효과를 확실히 느낌</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>확실한 활력 체감 효과 — 바쁘고 힘들 때 미리 먹으면 확실한 활력 증진 효과를 체감함.</t>
+          <t>신속하고 양호한 배송 — 배송 속도가 빠르고 배송 상태가 매우 양호함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>약 맛이 느껴지는 호불호 — 오렌지맛 감기약과 유사한 맛이 느껴져 맛 만족도는 다소 떨어짐.</t>
+          <t>호불호 갈리는 약 맛 — 오렌지 맛 감기약 느낌이 나 맛 부분에서는 호불호가 갈릴 수 있음</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -2103,18 +2099,18 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>우수한 가성비와 실속 — 유명 제품 대비 가격이 실속 있고 기대를 상회하는 효과를 보임.</t>
+          <t>뛰어난 가성비와 실속 — 타 유명 비타민 대비 합리적인 가격과 충실한 성분을 갖춤</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>빠른 컨디션 회복 체감 — 독감 및 피로 누적 등으로 컨디션이 저하되었을 때 빠른 회복을 도움.</t>
+          <t>빠른 컨디션 회복 — 독감이나 피로 누적 시 복용하면 빠른 체력 회복에 도움됨</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>쇼핑백 누락 배송 — 기본 구성품인 쇼핑백이 누락된 상태로 배송됨.</t>
+          <t>동봉 쇼핑백 누락 — 선물용 쇼핑백이 포함되지 않은 상태로 배송되는 경우가 있음</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -2162,17 +2158,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>휴대 용이한 개별 포장 — 개별 포장되어 가방에 넣고 외출할 때 휴대하기 용이함.</t>
+          <t>외출 시 편리한 개별 포장 — 한 포씩 개별 포장되어 가방에 휴대하며 음주 전후 챙기기 편함</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>탁월한 숙취 해소 효과 — 음주 전후 섭취 시 속이 편안하고 숙취가 적어 회복이 빠름.</t>
+          <t>뛰어난 숙취 완화 효과 — 음주 전후에 복용 시 다음날 숙취 완화 및 속 편안함 유지</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>알찬 선물세트 패키지 — 수량이 넉넉하고 예쁜 선물세트 구성으로 지인 선물에 적합함.</t>
+          <t>넉넉한 3세트 구성 — 총 15포의 넉넉한 분량과 깔끔한 포장으로 선물용에 적합함</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2221,25 +2217,21 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>더부룩함 완화 및 소화 도움 — 음식 복용 후 속 더부룩함이 사라지고 소화가 잘됨.</t>
+          <t>속 더부룩함 및 소화 개선 — 기름지거나 밀가루 음식 섭취 후 더부룩한 속을 편하게 해줌</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>고소하고 맛있는 풍미 — 달콤하고 고소한 풍미가 있어 맛있게 먹을 수 있음.</t>
+          <t>고소하고 달콤한 풍미 — 달콤하면서 고소한 맛이 나 거부감 없이 복용하기 용이함</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>용량 감소 및 맛 변화 — 리뉴얼 전 제품에 비해 용량이 줄고 맛이 달라짐.</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>다소 강한 단맛 — 단맛이 다소 강하게 느껴져 단맛 조절이 필요함.</t>
-        </is>
-      </c>
+          <t>용량 줄어듦 및 단맛 과다 — 기존 제품 대비 용량이 줄고 단맛이 조금 강하게 느껴질 수 있음</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
     </row>
     <row r="14" ht="38" customHeight="1">
@@ -2253,7 +2245,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) + 9포 추가증정</t>
+          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2263,39 +2255,39 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>44,500원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180343</t>
+          <t>https://gift.kakao.com/product/14208051</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261026140618_d8294b0175c344218da6d62160aa60a0.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261001090325_278bae1c2a364ec2a56a72260f627cdc.jpg</t>
         </is>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>1770</v>
+        <v>286</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>속 편한 소화 및 배변 도움 — 더부룩한 속을 편안하게 해주고 배변 활동을 도움.</t>
+          <t>다양하고 맛있는 맛 구성 — 베리말차, 크림소다 등 효소 거부감 없이 맛있게 즐길 수 있음</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>고소한 미숫가루 맛 — 텁텁함 없이 미숫가루처럼 고소하고 맛이 좋음.</t>
+          <t>만족스러운 사은품 구성 — 포토카드, 단백질바 등 알찬 증정품이 포함되어 만족도가 높음</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>증정 기프티콘 안내 부족 — 증정 기프티콘에 대한 수령 및 확인 방법 안내가 명확하지 않음.</t>
+          <t>포토카드 훼손 배송 — 포장 상태 불량으로 동봉된 포토카드가 구겨져 배송되는 문제 발생</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -2312,7 +2304,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) + 9포 추가증정</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2322,39 +2314,39 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>24,900원</t>
+          <t>44,500원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/14208051</t>
+          <t>https://gift.kakao.com/product/13180343</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261001090325_278bae1c2a364ec2a56a72260f627cdc.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261026140618_d8294b0175c344218da6d62160aa60a0.jpg</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>286</v>
+        <v>1770</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>거부감 없는 다양한 맛 — 효소 특유의 역함 없이 크림소다, 카카오 등 다양한 맛이 맛있음.</t>
+          <t>속 편안함 및 배변 도움 — 소화 불량 완화와 더불어 꾸준한 복용 시 아침 배변이 편안해짐</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>알찬 굿즈 및 사은품 구성 — 모델 포토카드와 단백질바 등 알찬 사은품 및 구성품이 제공됨.</t>
+          <t>미숫가루 스타일 고소한 맛 — 텁텁하지 않고 미숫가루처럼 고소하여 물 없이도 섭취하기 편함</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>굿즈 포토카드 훼손 배송 — 동봉된 포토카드가 구겨진 상태로 도착하여 포장 주의가 필요함.</t>
+          <t>증정 기프티콘 확인 불가 — 이벤트로 제공되는 기프티콘 확인 위치나 방법 안내가 부족함</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
@@ -2402,18 +2394,18 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>고급스럽고 예쁜 포장 — 오간자 포장과 플리츠백 등 패키지가 매우 고급스럽고 예쁨.</t>
+          <t>고급스러운 전용 포장 — 오간자 및 플리츠백 고급 패키지로 개봉 시 높은 만족감을 줌</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>비린 맛 없는 간편한 복용 — 비린 맛 없이 맛있고 하루 한 병씩 챙겨 먹기 편함.</t>
+          <t>맛있는 섭취와 피부 개선 — 맛이 좋아 챙겨 먹기 쉽고 피부 수분과 탄력 유지에 도움을 줌</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>선물 포장 누락 배송 — 안내와 달리 오간자 선물 포장이 누락된 채 배송됨.</t>
+          <t>오간자 선물 포장 누락 — 상품 설명과 달리 오간자 포장이 적용되지 않은 채 배송되는 경우 있음</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
@@ -2430,43 +2422,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나</t>
+          <t>BEST다모였닭 허닭 닭가슴살 다양하게 즐기기 20종 패키지</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>셀렉스</t>
+          <t>허닭</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>31,900원</t>
+          <t>27,900원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13550266</t>
+          <t>https://gift.kakao.com/product/1115219</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20250905115609_5450753e060a41638bfa377ba344c7c2.jpg</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>221</v>
+        <v>1931</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>비린 맛 없는 음료 같은 맛 — 단백질 특유의 비린 맛이 없고 달콤하여 음료처럼 마시기 좋음.</t>
+          <t>질리지 않는 20종 구성 — 다양한 맛과 종류로 구성되어 식단 진행 시 질리지 않음</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>든든한 포만감 제공 — 운동 후 마시면 포만감이 지속되어 간식 대용으로 활용하기 적절함.</t>
+          <t>촉촉한 식감과 간편 조리 — 퍽퍽하지 않고 촉촉하며 전용 용기가 제공되어 전자레인지 조리가 용이함</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -2485,50 +2477,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BEST다모였닭 허닭 닭가슴살 다양하게 즐기기 20종 패키지</t>
+          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>허닭</t>
+          <t>셀렉스</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>27,900원</t>
+          <t>31,900원</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/1115219</t>
+          <t>https://gift.kakao.com/product/13550266</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20250905115609_5450753e060a41638bfa377ba344c7c2.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>1931</v>
+        <v>221</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>질리지 않는 20종 구성 — 20종의 다양한 종류로 구성되어 질리지 않고 섭취 가능함.</t>
+          <t>비린 맛 없는 달콤한 맛 — 단백질 특유의 거부감이 없고 달콤한 음료처럼 맛있게 마실 수 있음</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>촉촉한 식감과 조리 편의성 — 닭가슴살이 촉촉하고 부드러우며 전용 용기가 포함되어 조리가 간편함.</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>꼼꼼한 신선 배송 — 아이스팩을 동봉하여 신선하게 포장 배송됨.</t>
-        </is>
-      </c>
+          <t>적절한 포만감과 단백질 — 운동 후 단백질 섭취에 용이하며 은근한 포만감으로 간식 대용 가능</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -2544,56 +2532,48 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>단백이 계란흰자 에그 프로틴 40개입(달걀 단백질 간편식)+(증정)단백이 구운맛 2개</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>가농</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>39,000원</t>
+          <t>64,200원</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/14380726</t>
+          <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261021165641_99634da9bf9f4b3d8e560929369229b1.png</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>흰자만 구성된 편리함 — 껍질을 까는 번거로움이 없고 계란 흰자만 있어 비리거나 퍽퍽하지 않음.</t>
+          <t>촉촉한 식감과 다양한 맛 — 닭가슴살이 촉촉하며 풍부한 맛 구성으로 질리지 않고 섭취 가능함</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>저칼로리 고포만감 — 칼로리가 낮아 다이어트 식단 및 야간 간식으로 포만감을 얻기 좋음.</t>
+          <t>전자레인지 간편 조리 — 전자레인지로 손쉽게 데워 먹을 수 있어 식사 대용으로 편리함</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>박스 포장 위생 아쉬움 — 포장 박스가 깨끗하지 않고 재활용한 느낌을 줌.</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>혼합 맛 구성 부재 — 다양한 맛을 한 번에 구매할 수 있는 혼합 옵션이 없음.</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
     </row>
     <row r="20" ht="38" customHeight="1">
@@ -2607,43 +2587,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
+          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템 (아르기닌+글리펌프 1포증정)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>삼대오백</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>64,200원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12860133</t>
+          <t>https://gift.kakao.com/product/6352718</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261020094546_5a86ba631cde44229cc1ed845bd1af8f.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>73</v>
+        <v>1956</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>촉촉한 식감과 풍부한 맛 — 퍽퍽하지 않고 촉촉하며 떡볶이맛 등 양념이 잘 어우러짐.</t>
+          <t>우수한 융해성과 입자 — 입자가 매우 고와서 물에 깔끔하게 잘 녹음</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>간편 조리 및 식단 관리 — 전자레인지에 간단히 데워 먹기 좋고 저칼로리로 식단 관리에 유용함.</t>
+          <t>운동 능력 향상 및 가성비 — 피로 감소와 운동 수행 능력 개선에 도움을 주며 대용량 가성비가 훌륭함</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -2693,19 +2673,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>초고함량 활력 충전 — 1포당 6,200mg의 고함량으로 피로 해소와 운동 전 활력 충전에 효과적임.</t>
+          <t>초고함량 활력 증진 — 높은 아르기닌 함량으로 피로 회복 및 운동 체력 증진 효과가 뛰어남</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1포 섭취의 간편성 — 하루 1포로 간편하고 개별 포장되어 휴대성이 우수함.</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>고급스러운 선물용 패키지 — 고급 패키지에 쇼핑백과 추가 증정포가 포함되어 선물용으로 훌륭함.</t>
-        </is>
-      </c>
+          <t>1포 개별 포장의 편의성 — 스틱 개별 포장으로 휴대 및 섭취가 간편하며 고급 패키지 구성됨</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -2898,12 +2874,12 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>뉴트리포유</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>오쏘몰</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>뉴트리포유</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -2935,7 +2911,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 로네펠트 기프트 에디션 (티백 5종증정)</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 단독 기프트박스 증정 (공식수입)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -2955,12 +2931,12 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
+          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
           <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 슬리브 기프트 에디션 (공식수입)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -3028,25 +3004,25 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16366</v>
+        <v>16368</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15709</v>
+        <v>15710</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3427</v>
+        <v>3429</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>6543</v>
       </c>
       <c r="G7" s="3" t="n">
+        <v>8769</v>
+      </c>
+      <c r="H7" s="3" t="n">
         <v>835</v>
       </c>
-      <c r="H7" s="3" t="n">
-        <v>8768</v>
-      </c>
       <c r="I7" s="3" t="n">
-        <v>1818</v>
+        <v>1820</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>105</v>
@@ -3066,66 +3042,64 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>우수한 피로 회복 효과 — 피로 누적 시 아침에 섭취하면 하루 종일 지치지 않는 우수한 체감을 제공함.
-고급스러운 포장 디자인 — 패키지 포장이 고급스러워 생일이나 특별한 날 선물용으로 적절함.</t>
+          <t>우수한 피로 회복 효과 — 피로 누적 시 아침 식후 복용 시 하루 종일 활력 유지 효과 체감
+고급 포장 및 빠른 배송 — 패키지 포장이 고급스럽고 배송이 깔끔하며 속도가 빠름</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>자극 없는 목넘김과 맛 — 영양제 신맛이 강하지 않고 목넘김이 부드러워 섭취하기 편함.
-피로 회복 및 활력 충전 — 피로할 때 복용하면 활력이 충전되고 구내염 개선에 도움을 줌.
-세련된 디자인과 휴대성 — 디자인이 세련되고 통 형태로 되어 있어 휴대하며 챙겨 먹기 유용함.</t>
+          <t>간편한 휴대 및 복용 — 액상과 정제 결합 포장으로 어디서나 간편하게 섭취 가능함
+부드러운 목넘김과 풍미 — 신맛이 강하지 않고 알약 섭취 시 목넘김이 부드러움
+피로 개선 및 구내염 완화 — 피로 회복과 몸 상태 개선, 구내염 완화에 도움을 줌</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>넉넉한 용량과 온가족 섭취 — 용량이 넉넉하여 온 가족이 함께 나누어 먹기에 적합함.
-확실한 활력 증진 효과 — 에너지를 올려주고 체력이 달릴 때 확실하게 힘이 나는 효과가 있음.
-진한 액상 농도 — 타 액상 제품에 비해 농도가 확실히 진하여 품질 만족도가 높음.</t>
+          <t>하루 한 병의 간편한 섭취 — 여러 영양제를 별도로 챙길 필요 없이 하루 한 병으로 해결됨
+진한 액상과 에너지 충전 — 액상 농도가 매우 진하며 지칠 때 먹으면 피로 회복 체감이 뛰어남
+넉넉한 용량 구성 — 30+3입 구성으로 한 달 이상 온 가족이 충분히 복용 가능함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>맛있고 간편한 젤리 형태 — 물 없이 간식처럼 씹어 먹는 새콤달콤한 젤리 형태로 섭취가 간편함.
-꾸준한 영양 관리 용이 — 영양제 먹는 것을 자주 잊는 사람도 매일 부담 없이 챙겨 먹기 좋음.</t>
+          <t>물 없이 먹는 젤리 타입 — 알약과 달리 물 없이 간식처럼 씹어 먹을 수 있어 편함
+새콤달콤하고 맛있는 풍미 — 은은한 단맛과 새콤달콤함으로 매일 맛있게 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>효과적인 피로 회복 — 피로 회복에 도움을 주며 환절기 체력 관리에 효과적임.
-알약과 액상 이중 제형 — 알약과 액상이 함께 구성되어 한 번에 간편하고 효과적인 섭취가 가능함.
-만족스러운 선물 구성 — 제품 구성과 배송 상태가 만족스러워 선물용으로 적합함.</t>
+          <t>합리적인 가격과 빠른 배송 — 좋은 제품을 착한 가격에 구매 가능하며 빠른 배송이 이뤄짐
+간편한 활력 충전 — 하루를 시작할 때 간편하게 복용하여 활력과 체력을 챙기기 좋음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>신속하고 안전한 배송 — 주문 후 제품 배송이 매우 빠르고 안전하게 도착함.
-간편한 피로 및 체력 관리 — 아침 출근길이나 피곤할 때 간편하게 먹고 활력을 얻기 좋음.</t>
+          <t>정제와 액상의 이중 제형 — 알약과 액상 비타민이 함께 들어있어 높은 효과가 느껴짐
+환절기 피로 회복 체감 — 환절기 건강 관리 및 피로 회복에 빠른 체감 효과를 선사함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>신기한 분말 혼합 제형 — 버튼을 눌러 분말을 액상에 풀어 마시는 신기한 방식임.
-우수한 휴대성과 간편함 — 가방에 넣어 다니다가 피곤할 때 간편하게 챙겨 먹기 유용함.
-고급스러운 브랜드 이미지 — 정관장 브랜드로 포장과 분위기가 고급스러워 선물용으로 적합함.</t>
+          <t>목걸림 없는 분말 제형 — 알약과 달리 분말을 액상에 풀어 마셔 목에 걸리는 불편함이 없음
+우수한 휴대성과 활력 증진 — 가방에 넣어 다니기 좋으며 피곤할 때 복용 시 에너지 생성을 도움</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>개별 포장의 우수한 휴대성 — 컴팩트한 포 포장으로 여행이나 외출 시 가방에 들고 다니기 좋음.
-체력 증진 및 활력 제공 — 꾸준히 복용 시 활력이 생기고 피로 해소에 도움을 줌.</t>
+          <t>휴대가 용이한 포장 형태 — 개별 포 형태로 제작되어 여행이나 외출 시 휴대가 매우 편리함
+지속 복용 시 에너지 개선 — 일주일 정도 꾸준히 섭취 시 몸에 활력이 생기는 것을 체감함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>빠르고 안전한 배송 — 배송 상태가 양호하고 신속하게 도착함.
-확실한 활력 체감 효과 — 바쁘고 힘들 때 미리 먹으면 확실한 활력 증진 효과를 체감함.</t>
+          <t>확실한 활력 증진 효과 — 바쁘고 피로할 때 복용 시 몸에 활력이 돋는 효과를 확실히 느낌
+신속하고 양호한 배송 — 배송 속도가 빠르고 배송 상태가 매우 양호함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>우수한 가성비와 실속 — 유명 제품 대비 가격이 실속 있고 기대를 상회하는 효과를 보임.
-빠른 컨디션 회복 체감 — 독감 및 피로 누적 등으로 컨디션이 저하되었을 때 빠른 회복을 도움.</t>
+          <t>뛰어난 가성비와 실속 — 타 유명 비타민 대비 합리적인 가격과 충실한 성분을 갖춤
+빠른 컨디션 회복 — 독감이나 피로 누적 시 복용하면 빠른 체력 회복에 도움됨</t>
         </is>
       </c>
     </row>
@@ -3137,10 +3111,14 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>공복 섭취 시 속쓰림 발생 — 고함량 제품 특성상 공복에 복용 시 속쓰림이나 울렁거림이 심하게 발생할 수 있음.</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr"/>
+          <t>공복 복용 시 위장 장애 — 고함량 영양제 특성상 빈속에 먹으면 속쓰림이나 울렁거림 발생 가능</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>단기 복용 시 미미한 체감 — 며칠 안 먹은 초기에는 즉각적인 변화 효과 체감이 적을 수 있음</t>
+        </is>
+      </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
@@ -3148,18 +3126,18 @@
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>배송 중 박스 구겨짐 — 배송 과정에서 박스가 다 구겨져서 도착한 점이 아쉬움.
-아쉬운 사은품 품질 — 함께 제공된 사은품의 품질이 기대에 미치지 못함.</t>
+          <t>배송 상자 구겨짐 발생 — 배송 과정 중에 제품 외관 박스가 구겨져서 도착하는 문제 있음
+아쉬운 사은품 품질 — 동봉되어 오는 사은품이 저가형 제품으로 제공되어 다소 아쉬움</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>약 맛이 느껴지는 호불호 — 오렌지맛 감기약과 유사한 맛이 느껴져 맛 만족도는 다소 떨어짐.</t>
+          <t>호불호 갈리는 약 맛 — 오렌지 맛 감기약 느낌이 나 맛 부분에서는 호불호가 갈릴 수 있음</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>쇼핑백 누락 배송 — 기본 구성품인 쇼핑백이 누락된 상태로 배송됨.</t>
+          <t>동봉 쇼핑백 누락 — 선물용 쇼핑백이 포함되지 않은 상태로 배송되는 경우가 있음</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3149,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>35,900원</t>
+          <t>34,000원</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -3191,12 +3169,12 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
+          <t>19,900원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
           <t>43,900원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>19,900원</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -3441,22 +3419,22 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
+          <t>허닭</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
           <t>셀렉스</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>허닭</t>
-        </is>
-      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>가농</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>삼대오백</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -3483,14 +3461,14 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
+          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
           <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) + 9포 추가증정</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
-        </is>
-      </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
           <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
@@ -3498,22 +3476,22 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
+          <t>BEST다모였닭 허닭 닭가슴살 다양하게 즐기기 20종 패키지</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
           <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>BEST다모였닭 허닭 닭가슴살 다양하게 즐기기 20종 패키지</t>
-        </is>
-      </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>단백이 계란흰자 에그 프로틴 40개입(달걀 단백질 간편식)+(증정)단백이 구운맛 2개</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
+          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템 (아르기닌+글리펌프 1포증정)</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -3572,25 +3550,25 @@
         <v>982</v>
       </c>
       <c r="E19" s="3" t="n">
+        <v>286</v>
+      </c>
+      <c r="F19" s="3" t="n">
         <v>1770</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>286</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>763</v>
       </c>
       <c r="H19" s="3" t="n">
+        <v>1931</v>
+      </c>
+      <c r="I19" s="3" t="n">
         <v>221</v>
       </c>
-      <c r="I19" s="3" t="n">
-        <v>1931</v>
-      </c>
       <c r="J19" s="3" t="n">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>73</v>
+        <v>1956</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>250</v>
@@ -3604,69 +3582,67 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>휴대 용이한 개별 포장 — 개별 포장되어 가방에 넣고 외출할 때 휴대하기 용이함.
-탁월한 숙취 해소 효과 — 음주 전후 섭취 시 속이 편안하고 숙취가 적어 회복이 빠름.
-알찬 선물세트 패키지 — 수량이 넉넉하고 예쁜 선물세트 구성으로 지인 선물에 적합함.</t>
+          <t>외출 시 편리한 개별 포장 — 한 포씩 개별 포장되어 가방에 휴대하며 음주 전후 챙기기 편함
+뛰어난 숙취 완화 효과 — 음주 전후에 복용 시 다음날 숙취 완화 및 속 편안함 유지
+넉넉한 3세트 구성 — 총 15포의 넉넉한 분량과 깔끔한 포장으로 선물용에 적합함</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>더부룩함 완화 및 소화 도움 — 음식 복용 후 속 더부룩함이 사라지고 소화가 잘됨.
-고소하고 맛있는 풍미 — 달콤하고 고소한 풍미가 있어 맛있게 먹을 수 있음.</t>
+          <t>속 더부룩함 및 소화 개선 — 기름지거나 밀가루 음식 섭취 후 더부룩한 속을 편하게 해줌
+고소하고 달콤한 풍미 — 달콤하면서 고소한 맛이 나 거부감 없이 복용하기 용이함</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>속 편한 소화 및 배변 도움 — 더부룩한 속을 편안하게 해주고 배변 활동을 도움.
-고소한 미숫가루 맛 — 텁텁함 없이 미숫가루처럼 고소하고 맛이 좋음.</t>
+          <t>다양하고 맛있는 맛 구성 — 베리말차, 크림소다 등 효소 거부감 없이 맛있게 즐길 수 있음
+만족스러운 사은품 구성 — 포토카드, 단백질바 등 알찬 증정품이 포함되어 만족도가 높음</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>거부감 없는 다양한 맛 — 효소 특유의 역함 없이 크림소다, 카카오 등 다양한 맛이 맛있음.
-알찬 굿즈 및 사은품 구성 — 모델 포토카드와 단백질바 등 알찬 사은품 및 구성품이 제공됨.</t>
+          <t>속 편안함 및 배변 도움 — 소화 불량 완화와 더불어 꾸준한 복용 시 아침 배변이 편안해짐
+미숫가루 스타일 고소한 맛 — 텁텁하지 않고 미숫가루처럼 고소하여 물 없이도 섭취하기 편함</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>고급스럽고 예쁜 포장 — 오간자 포장과 플리츠백 등 패키지가 매우 고급스럽고 예쁨.
-비린 맛 없는 간편한 복용 — 비린 맛 없이 맛있고 하루 한 병씩 챙겨 먹기 편함.</t>
+          <t>고급스러운 전용 포장 — 오간자 및 플리츠백 고급 패키지로 개봉 시 높은 만족감을 줌
+맛있는 섭취와 피부 개선 — 맛이 좋아 챙겨 먹기 쉽고 피부 수분과 탄력 유지에 도움을 줌</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>비린 맛 없는 음료 같은 맛 — 단백질 특유의 비린 맛이 없고 달콤하여 음료처럼 마시기 좋음.
-든든한 포만감 제공 — 운동 후 마시면 포만감이 지속되어 간식 대용으로 활용하기 적절함.</t>
+          <t>질리지 않는 20종 구성 — 다양한 맛과 종류로 구성되어 식단 진행 시 질리지 않음
+촉촉한 식감과 간편 조리 — 퍽퍽하지 않고 촉촉하며 전용 용기가 제공되어 전자레인지 조리가 용이함</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>질리지 않는 20종 구성 — 20종의 다양한 종류로 구성되어 질리지 않고 섭취 가능함.
-촉촉한 식감과 조리 편의성 — 닭가슴살이 촉촉하고 부드러우며 전용 용기가 포함되어 조리가 간편함.
-꼼꼼한 신선 배송 — 아이스팩을 동봉하여 신선하게 포장 배송됨.</t>
+          <t>비린 맛 없는 달콤한 맛 — 단백질 특유의 거부감이 없고 달콤한 음료처럼 맛있게 마실 수 있음
+적절한 포만감과 단백질 — 운동 후 단백질 섭취에 용이하며 은근한 포만감으로 간식 대용 가능</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>흰자만 구성된 편리함 — 껍질을 까는 번거로움이 없고 계란 흰자만 있어 비리거나 퍽퍽하지 않음.
-저칼로리 고포만감 — 칼로리가 낮아 다이어트 식단 및 야간 간식으로 포만감을 얻기 좋음.</t>
+          <t>촉촉한 식감과 다양한 맛 — 닭가슴살이 촉촉하며 풍부한 맛 구성으로 질리지 않고 섭취 가능함
+전자레인지 간편 조리 — 전자레인지로 손쉽게 데워 먹을 수 있어 식사 대용으로 편리함</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>촉촉한 식감과 풍부한 맛 — 퍽퍽하지 않고 촉촉하며 떡볶이맛 등 양념이 잘 어우러짐.
-간편 조리 및 식단 관리 — 전자레인지에 간단히 데워 먹기 좋고 저칼로리로 식단 관리에 유용함.</t>
+          <t>우수한 융해성과 입자 — 입자가 매우 고와서 물에 깔끔하게 잘 녹음
+운동 능력 향상 및 가성비 — 피로 감소와 운동 수행 능력 개선에 도움을 주며 대용량 가성비가 훌륭함</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>초고함량 활력 충전 — 1포당 6,200mg의 고함량으로 피로 해소와 운동 전 활력 충전에 효과적임.
-1포 섭취의 간편성 — 하루 1포로 간편하고 개별 포장되어 휴대성이 우수함.
-고급스러운 선물용 패키지 — 고급 패키지에 쇼핑백과 추가 증정포가 포함되어 선물용으로 훌륭함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
+          <t>초고함량 활력 증진 — 높은 아르기닌 함량으로 피로 회복 및 운동 체력 증진 효과가 뛰어남
+1포 개별 포장의 편의성 — 스틱 개별 포장으로 휴대 및 섭취가 간편하며 고급 패키지 구성됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
       <c r="B21" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -3675,33 +3651,27 @@
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>용량 감소 및 맛 변화 — 리뉴얼 전 제품에 비해 용량이 줄고 맛이 달라짐.
-다소 강한 단맛 — 단맛이 다소 강하게 느껴져 단맛 조절이 필요함.</t>
+          <t>용량 줄어듦 및 단맛 과다 — 기존 제품 대비 용량이 줄고 단맛이 조금 강하게 느껴질 수 있음</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>증정 기프티콘 안내 부족 — 증정 기프티콘에 대한 수령 및 확인 방법 안내가 명확하지 않음.</t>
+          <t>포토카드 훼손 배송 — 포장 상태 불량으로 동봉된 포토카드가 구겨져 배송되는 문제 발생</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>굿즈 포토카드 훼손 배송 — 동봉된 포토카드가 구겨진 상태로 도착하여 포장 주의가 필요함.</t>
+          <t>증정 기프티콘 확인 불가 — 이벤트로 제공되는 기프티콘 확인 위치나 방법 안내가 부족함</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>선물 포장 누락 배송 — 안내와 달리 오간자 선물 포장이 누락된 채 배송됨.</t>
+          <t>오간자 선물 포장 누락 — 상품 설명과 달리 오간자 포장이 적용되지 않은 채 배송되는 경우 있음</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>박스 포장 위생 아쉬움 — 포장 박스가 깨끗하지 않고 재활용한 느낌을 줌.
-혼합 맛 구성 부재 — 다양한 맛을 한 번에 구매할 수 있는 혼합 옵션이 없음.</t>
-        </is>
-      </c>
+      <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="inlineStr"/>
     </row>
@@ -3723,14 +3693,14 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
+          <t>24,900원</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
           <t>44,500원</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>24,900원</t>
-        </is>
-      </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
           <t>65,900원</t>
@@ -3738,22 +3708,22 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
+          <t>27,900원</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
           <t>31,900원</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>27,900원</t>
-        </is>
-      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>39,000원</t>
+          <t>64,200원</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>64,200원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -3933,7 +3903,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -3949,7 +3919,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B6" t="n">
